--- a/Assets/Config/Excel/MapSpawn.xlsx
+++ b/Assets/Config/Excel/MapSpawn.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\Project\Unity\CarrotFantasy\Assets\Config\Excel\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F09DE397-0CE0-480F-9290-23EDB8D00E82}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6F49AA54-B300-4845-874E-F2AD10634500}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-24120" yWindow="-120" windowWidth="24240" windowHeight="13140" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
